--- a/samples/Trial_Balance_AE_Jul-26.xlsx
+++ b/samples/Trial_Balance_AE_Jul-26.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D35"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>206677.94</v>
+        <v>909135.9</v>
       </c>
     </row>
     <row r="8">
@@ -464,7 +464,7 @@
         <v>Cash</v>
       </c>
       <c r="D8">
-        <v>386.38</v>
+        <v>374.79</v>
       </c>
     </row>
     <row r="9">
@@ -478,7 +478,7 @@
         <v>Accounts Receivable</v>
       </c>
       <c r="D9">
-        <v>130577.65</v>
+        <v>126660.32</v>
       </c>
     </row>
     <row r="10">
@@ -492,7 +492,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D10">
-        <v>8729.94</v>
+        <v>8468.04</v>
       </c>
     </row>
     <row r="11">
@@ -506,7 +506,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D11">
-        <v>6858.17</v>
+        <v>6652.42</v>
       </c>
     </row>
     <row r="12">
@@ -520,7 +520,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D12">
-        <v>16055.25</v>
+        <v>15573.59</v>
       </c>
     </row>
     <row r="13">
@@ -534,7 +534,7 @@
         <v>Fixed Asset</v>
       </c>
       <c r="D13">
-        <v>67672.35</v>
+        <v>65642.18</v>
       </c>
     </row>
     <row r="14">
@@ -548,7 +548,7 @@
         <v>Fixed Asset</v>
       </c>
       <c r="D14">
-        <v>-25024.05</v>
+        <v>-24273.33</v>
       </c>
     </row>
     <row r="15">
@@ -562,7 +562,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D15">
-        <v>4203.4</v>
+        <v>4077.3</v>
       </c>
     </row>
     <row r="16">
@@ -576,7 +576,7 @@
         <v>Accounts Payable</v>
       </c>
       <c r="D16">
-        <v>-38460.11</v>
+        <v>-37306.31</v>
       </c>
     </row>
     <row r="17">
@@ -590,7 +590,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D17">
-        <v>-19721.33</v>
+        <v>-19129.69</v>
       </c>
     </row>
     <row r="18">
@@ -604,7 +604,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D18">
-        <v>-9484.53</v>
+        <v>-9199.99</v>
       </c>
     </row>
     <row r="19">
@@ -618,202 +618,230 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D19">
-        <v>-7617.28</v>
+        <v>-7388.76</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>3001</v>
+        <v>2300</v>
       </c>
       <c r="B20" t="str">
-        <v>Equity Share Capital</v>
+        <v>Due to Aistra GenAI India Pvt Ltd</v>
       </c>
       <c r="C20" t="str">
-        <v>Equity</v>
+        <v>Other Current Liability</v>
       </c>
       <c r="D20">
-        <v>-166088.81</v>
+        <v>-281300</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>3100</v>
+        <v>3001</v>
       </c>
       <c r="B21" t="str">
-        <v>Securities Premium</v>
+        <v>Equity Share Capital</v>
       </c>
       <c r="C21" t="str">
         <v>Equity</v>
       </c>
       <c r="D21">
-        <v>-88668.84</v>
+        <v>-550000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>3200</v>
+        <v>3100</v>
       </c>
       <c r="B22" t="str">
-        <v>Retained Earnings</v>
+        <v>Securities Premium</v>
       </c>
       <c r="C22" t="str">
         <v>Equity</v>
       </c>
       <c r="D22">
-        <v>-45547.78</v>
+        <v>-250000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>4001</v>
+        <v>3200</v>
       </c>
       <c r="B23" t="str">
-        <v>Consulting Revenue</v>
+        <v>Retained Earnings</v>
       </c>
       <c r="C23" t="str">
-        <v>Income</v>
+        <v>Equity</v>
       </c>
       <c r="D23">
-        <v>-334723.11</v>
+        <v>-45547.78</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>4500</v>
+        <v>4001</v>
       </c>
       <c r="B24" t="str">
-        <v>Interest Income</v>
+        <v>Consulting Revenue</v>
       </c>
       <c r="C24" t="str">
-        <v>Other Income</v>
+        <v>Income</v>
       </c>
       <c r="D24">
-        <v>-2105.88</v>
+        <v>-267778.49</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>5001</v>
+        <v>4500</v>
       </c>
       <c r="B25" t="str">
-        <v>Cost of Services</v>
+        <v>Interest Income</v>
       </c>
       <c r="C25" t="str">
-        <v>Cost Of Goods Sold</v>
+        <v>Other Income</v>
       </c>
       <c r="D25">
-        <v>121335.07</v>
+        <v>-1684.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>6001</v>
+        <v>5001</v>
       </c>
       <c r="B26" t="str">
-        <v>Salaries and Wages</v>
+        <v>Cost of Services</v>
       </c>
       <c r="C26" t="str">
-        <v>Expense</v>
+        <v>Cost Of Goods Sold</v>
       </c>
       <c r="D26">
-        <v>104544.4</v>
+        <v>97068.06</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>6100</v>
+        <v>6001</v>
       </c>
       <c r="B27" t="str">
-        <v>Travel and Conveyance</v>
+        <v>Salaries and Wages</v>
       </c>
       <c r="C27" t="str">
         <v>Expense</v>
       </c>
       <c r="D27">
-        <v>9724.49</v>
+        <v>83635.52</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>6200</v>
+        <v>6100</v>
       </c>
       <c r="B28" t="str">
-        <v>Professional Fees</v>
+        <v>Travel and Conveyance</v>
       </c>
       <c r="C28" t="str">
         <v>Expense</v>
       </c>
       <c r="D28">
-        <v>13730.01</v>
+        <v>7779.59</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>6300</v>
+        <v>6200</v>
       </c>
       <c r="B29" t="str">
-        <v>Software Subscriptions</v>
+        <v>Professional Fees</v>
       </c>
       <c r="C29" t="str">
         <v>Expense</v>
       </c>
       <c r="D29">
-        <v>10686.98</v>
+        <v>10984.01</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>6400</v>
+        <v>6300</v>
       </c>
       <c r="B30" t="str">
-        <v>Rent</v>
+        <v>Software Subscriptions</v>
       </c>
       <c r="C30" t="str">
         <v>Expense</v>
       </c>
       <c r="D30">
-        <v>17552.86</v>
+        <v>8549.58</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>6500</v>
+        <v>6400</v>
       </c>
       <c r="B31" t="str">
-        <v>Depreciation</v>
+        <v>Rent</v>
       </c>
       <c r="C31" t="str">
         <v>Expense</v>
       </c>
       <c r="D31">
-        <v>5862.63</v>
+        <v>14042.29</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>6900</v>
+        <v>6500</v>
       </c>
       <c r="B32" t="str">
-        <v>Income Tax Expense</v>
+        <v>Depreciation</v>
       </c>
       <c r="C32" t="str">
         <v>Expense</v>
       </c>
       <c r="D32">
-        <v>12844.2</v>
+        <v>4690.1</v>
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="str">
+        <v>6600</v>
+      </c>
       <c r="B33" t="str">
+        <v>IC Service Charges - India</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D33">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>6900</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Income Tax Expense</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="D34">
+        <v>10275.36</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="str">
         <v>Total</v>
       </c>
-      <c r="D33">
+      <c r="D35">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D33"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D35"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/samples/Trial_Balance_AE_Jul-26.xlsx
+++ b/samples/Trial_Balance_AE_Jul-26.xlsx
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>909135.9</v>
+        <v>1014697.22</v>
       </c>
     </row>
     <row r="8">
@@ -688,7 +688,7 @@
         <v>Income</v>
       </c>
       <c r="D24">
-        <v>-267778.49</v>
+        <v>-232522.29</v>
       </c>
     </row>
     <row r="25">
@@ -702,7 +702,7 @@
         <v>Other Income</v>
       </c>
       <c r="D25">
-        <v>-1684.7</v>
+        <v>-532.01</v>
       </c>
     </row>
     <row r="26">
@@ -716,7 +716,7 @@
         <v>Cost Of Goods Sold</v>
       </c>
       <c r="D26">
-        <v>97068.06</v>
+        <v>29067.37</v>
       </c>
     </row>
     <row r="27">
@@ -730,7 +730,7 @@
         <v>Expense</v>
       </c>
       <c r="D27">
-        <v>83635.52</v>
+        <v>25117.15</v>
       </c>
     </row>
     <row r="28">
@@ -744,7 +744,7 @@
         <v>Expense</v>
       </c>
       <c r="D28">
-        <v>7779.59</v>
+        <v>2333.88</v>
       </c>
     </row>
     <row r="29">
@@ -758,7 +758,7 @@
         <v>Expense</v>
       </c>
       <c r="D29">
-        <v>10984.01</v>
+        <v>3295.2</v>
       </c>
     </row>
     <row r="30">
@@ -772,7 +772,7 @@
         <v>Expense</v>
       </c>
       <c r="D30">
-        <v>8549.58</v>
+        <v>2538.43</v>
       </c>
     </row>
     <row r="31">
@@ -786,7 +786,7 @@
         <v>Expense</v>
       </c>
       <c r="D31">
-        <v>14042.29</v>
+        <v>4239.18</v>
       </c>
     </row>
     <row r="32">
@@ -800,7 +800,7 @@
         <v>Expense</v>
       </c>
       <c r="D32">
-        <v>4690.1</v>
+        <v>1380.48</v>
       </c>
     </row>
     <row r="33">
@@ -814,7 +814,7 @@
         <v>Expense</v>
       </c>
       <c r="D33">
-        <v>120000</v>
+        <v>144000</v>
       </c>
     </row>
     <row r="34">
@@ -828,7 +828,7 @@
         <v>Expense</v>
       </c>
       <c r="D34">
-        <v>10275.36</v>
+        <v>3082.61</v>
       </c>
     </row>
     <row r="35">

--- a/samples/Trial_Balance_AE_Jul-26.xlsx
+++ b/samples/Trial_Balance_AE_Jul-26.xlsx
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>1014697.22</v>
+        <v>862455.38</v>
       </c>
     </row>
     <row r="8">
@@ -688,7 +688,7 @@
         <v>Income</v>
       </c>
       <c r="D24">
-        <v>-232522.29</v>
+        <v>-80280.45</v>
       </c>
     </row>
     <row r="25">
